--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_185_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_185_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2614</v>
+        <v>4.8827</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0556</v>
+        <v>4.2483</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2057</v>
+        <v>0.6344</v>
       </c>
       <c r="G2" t="n">
         <v>0.9856</v>
@@ -610,13 +610,13 @@
         <v>3.9432</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5619</v>
+        <v>-0.9405</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4778</v>
+        <v>-1.2852</v>
       </c>
       <c r="U2" t="n">
-        <v>0.916</v>
+        <v>0.3446</v>
       </c>
       <c r="V2" t="n">
         <v>2.2862</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.609</v>
+        <v>2.7833</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9393</v>
+        <v>1.1136</v>
       </c>
       <c r="F3" t="n">
         <v>1.6697</v>
@@ -688,10 +688,10 @@
         <v>3.7112</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7354000000000001</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6176</v>
+        <v>-0.208</v>
       </c>
       <c r="U3" t="n">
         <v>0.1177</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4266</v>
+        <v>0.5185</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3929</v>
+        <v>-0.2002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8195</v>
+        <v>0.7187</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3489</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4564</v>
+        <v>-0.3646</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9788</v>
+        <v>-0.4837</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0029</v>
+        <v>-0.8103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0241</v>
+        <v>0.3266</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3614</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0091</v>
+        <v>-0.514</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8962</v>
+        <v>-0.7035</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1129</v>
+        <v>0.1896</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7995</v>
+        <v>-2.0348</v>
       </c>
       <c r="E6" t="n">
         <v>-2.0364</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2369</v>
+        <v>0.0016</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2456</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.322</v>
+        <v>-0.5573</v>
       </c>
       <c r="T6" t="n">
         <v>-0.5975</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2754</v>
+        <v>0.0402</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3349</v>
+        <v>-3.0825</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.005</v>
+        <v>-2.8871</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3299</v>
+        <v>-0.1954</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4299</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4411</v>
+        <v>-0.1887</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6619</v>
+        <v>-3.2579</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.4466</v>
+        <v>-5.2107</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7847</v>
+        <v>1.9527</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6379</v>
@@ -1078,13 +1078,13 @@
         <v>3.2473</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7921</v>
+        <v>-0.3881</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1209</v>
+        <v>-3.7113</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4678</v>
+        <v>-2.9753</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6531</v>
+        <v>-0.736</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.96</v>
+        <v>-2.7776</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6986</v>
+        <v>-0.2413</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2614</v>
+        <v>-2.5363</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9509</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1646</v>
+        <v>1.6504</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7863</v>
+        <v>-2.3222</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0091</v>
+        <v>-2.1057</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.534</v>
+        <v>-1.8917</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4751</v>
+        <v>-0.214</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1586</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1221</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0365</v>
+        <v>0.0323</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2064</v>
+        <v>-4.6263</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.168</v>
+        <v>-3.9396</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0384</v>
+        <v>-0.6867</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7776</v>
+        <v>-2.96</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2413</v>
+        <v>-1.6986</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5363</v>
+        <v>-1.2614</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.9509</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6504</v>
+        <v>-0.1646</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3222</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1057</v>
+        <v>-2.0091</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8917</v>
+        <v>-1.534</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.214</v>
+        <v>-0.4751</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3746</v>
+        <v>-0.3468</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1044</v>
+        <v>-0.3497</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2702</v>
+        <v>0.0029</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0619</v>
+        <v>-4.9193</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2652</v>
+        <v>-5.9546</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2033</v>
+        <v>1.0353</v>
       </c>
       <c r="G11" t="n">
         <v>-5.241</v>
@@ -1312,13 +1312,13 @@
         <v>3.0154</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6585</v>
+        <v>-0.516</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1949</v>
+        <v>-0.8843</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6868</v>
+        <v>-7.2493</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.6914</v>
+        <v>-7.4555</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0046</v>
+        <v>0.2062</v>
       </c>
       <c r="G12" t="n">
         <v>-6.9997</v>
@@ -1390,13 +1390,13 @@
         <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.919</v>
+        <v>-0.4815</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5816</v>
+        <v>-0.3457</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.5541</v>
+        <v>-21.1806</v>
       </c>
       <c r="E13" t="n">
-        <v>-26.4813</v>
+        <v>-26.1078</v>
       </c>
       <c r="F13" t="n">
-        <v>4.927099999999999</v>
+        <v>4.9271</v>
       </c>
       <c r="G13" t="n">
         <v>-22.8387</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.346599999999999</v>
+        <v>-7.3466</v>
       </c>
       <c r="I13" t="n">
         <v>-15.4919</v>
@@ -1456,7 +1456,7 @@
         <v>-13.9291</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5534</v>
+        <v>-5.553399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>4.6392</v>
@@ -1468,13 +1468,13 @@
         <v>26.6745</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.640700000000001</v>
+        <v>-5.2673</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.2706</v>
+        <v>-6.897099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6298</v>
+        <v>1.6299</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1483,13 +1483,13 @@
         <v>6.180700000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8945</v>
+        <v>-3.894500000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1422</v>
+        <v>5.4798</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4722</v>
+        <v>2.6641</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6144</v>
+        <v>2.8158</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2527</v>
+        <v>5.9172</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1786</v>
+        <v>0.982</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0741</v>
+        <v>4.9353</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8953</v>
+        <v>5.9569</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2839</v>
+        <v>1.7512</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3887</v>
+        <v>4.2057</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3575</v>
+        <v>-0.0397</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1053</v>
+        <v>-0.7692</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4628</v>
+        <v>0.7296</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4793</v>
+        <v>3.2473</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7297</v>
+        <v>0.8667</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1202</v>
+        <v>-0.3497</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8499</v>
+        <v>1.2164</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8951</v>
+        <v>5.0541</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1922</v>
+        <v>-0.2363</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7029</v>
+        <v>5.2904</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9172</v>
+        <v>3.2527</v>
       </c>
       <c r="H15" t="n">
-        <v>0.982</v>
+        <v>2.1786</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9353</v>
+        <v>1.0741</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9569</v>
+        <v>1.8953</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7512</v>
+        <v>3.2839</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2057</v>
+        <v>-1.3887</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0397</v>
+        <v>1.3575</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7692</v>
+        <v>-1.1053</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7296</v>
+        <v>2.4628</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2473</v>
+        <v>3.4793</v>
       </c>
       <c r="S15" t="n">
-        <v>0.282</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8215</v>
+        <v>-0.8843</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1035</v>
+        <v>1.5259</v>
       </c>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X15" t="n">
         <v>-1.0722</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4138</v>
+        <v>3.8513</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.1326</v>
       </c>
       <c r="F16" t="n">
-        <v>2.517</v>
+        <v>2.7187</v>
       </c>
       <c r="G16" t="n">
         <v>1.9031</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0228</v>
+        <v>0.4147</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4252</v>
+        <v>0.6269</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3148</v>
+        <v>3.7187</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8093</v>
+        <v>1.0452</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5054</v>
+        <v>2.6735</v>
       </c>
       <c r="G17" t="n">
         <v>2.592</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0452</v>
+        <v>0.3587</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4028</v>
+        <v>0.5709</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0315</v>
+        <v>3.2812</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4321</v>
+        <v>3.8745</v>
       </c>
       <c r="F18" t="n">
-        <v>5.4635</v>
+        <v>-0.5933</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9701</v>
+        <v>1.3863</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5438</v>
+        <v>1.7141</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4263</v>
+        <v>-0.3279</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4765</v>
+        <v>1.7472</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3023</v>
+        <v>1.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1742</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4936</v>
+        <v>-0.3609</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7584</v>
+        <v>0.1141</v>
       </c>
       <c r="O18" t="n">
-        <v>2.252</v>
+        <v>-0.4751</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2473</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6128</v>
+        <v>0.9671</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>0.519</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7227</v>
+        <v>0.4481</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.973</v>
+        <v>3.1881</v>
       </c>
       <c r="E19" t="n">
-        <v>3.9925</v>
+        <v>-2.668</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0195</v>
+        <v>5.856</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3863</v>
+        <v>4.9701</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7141</v>
+        <v>1.5438</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3279</v>
+        <v>3.4263</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7472</v>
+        <v>3.4765</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6</v>
+        <v>2.3023</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1472</v>
+        <v>1.1742</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3609</v>
+        <v>1.4936</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1141</v>
+        <v>-0.7584</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4751</v>
+        <v>2.252</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>3.2473</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6589</v>
+        <v>0.7694</v>
       </c>
       <c r="T19" t="n">
-        <v>0.637</v>
+        <v>-0.3457</v>
       </c>
       <c r="U19" t="n">
-        <v>0.022</v>
+        <v>1.1152</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5564</v>
+        <v>2.2749</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7452</v>
+        <v>0.0375</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8113</v>
+        <v>2.2374</v>
       </c>
       <c r="G20" t="n">
         <v>0.8871</v>
@@ -2014,13 +2014,13 @@
         <v>2.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2054</v>
+        <v>0.9238</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7512</v>
+        <v>0.0435</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4542</v>
+        <v>0.8804</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2152</v>
+        <v>0.1702</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0022</v>
+        <v>-0.2337</v>
       </c>
       <c r="F21" t="n">
-        <v>0.213</v>
+        <v>0.4039</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0626</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6515</v>
+        <v>0.6065</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1211</v>
+        <v>-0.1363</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9213</v>
+        <v>-5.1572</v>
       </c>
       <c r="F22" t="n">
-        <v>5.0424</v>
+        <v>5.0209</v>
       </c>
       <c r="G22" t="n">
         <v>3.0834</v>
@@ -2170,13 +2170,13 @@
         <v>3.2473</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4269</v>
+        <v>1.1694</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U22" t="n">
-        <v>1.462</v>
+        <v>1.4405</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6778999999999999</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.109</v>
+        <v>-3.7551</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6675</v>
+        <v>-4.3136</v>
       </c>
       <c r="F23" t="n">
         <v>0.5585</v>
@@ -2248,10 +2248,10 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1415</v>
+        <v>0.4953</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U23" t="n">
         <v>0.5895</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.5541</v>
+        <v>23.1269</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.855</v>
+        <v>-3.8549</v>
       </c>
       <c r="F24" t="n">
-        <v>25.4089</v>
+        <v>26.9818</v>
       </c>
       <c r="G24" t="n">
         <v>22.8386</v>
@@ -2326,13 +2326,13 @@
         <v>22.0353</v>
       </c>
       <c r="S24" t="n">
-        <v>5.6407</v>
+        <v>7.213200000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6298</v>
+        <v>-1.6299</v>
       </c>
       <c r="U24" t="n">
-        <v>7.270300000000001</v>
+        <v>8.8432</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2862</v>
